--- a/output/yearly_population_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_55_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4635</v>
+        <v>5223</v>
       </c>
       <c r="C2" t="n">
-        <v>11239</v>
+        <v>11875</v>
       </c>
       <c r="D2" t="n">
-        <v>28320</v>
+        <v>29230</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2963</v>
+        <v>3696</v>
       </c>
       <c r="C3" t="n">
-        <v>5430</v>
+        <v>4351</v>
       </c>
       <c r="D3" t="n">
-        <v>17941</v>
+        <v>19082</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2457</v>
+        <v>2983</v>
       </c>
       <c r="C4" t="n">
-        <v>6714</v>
+        <v>4741</v>
       </c>
       <c r="D4" t="n">
-        <v>8125</v>
+        <v>8497</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1641</v>
+        <v>1909</v>
       </c>
       <c r="C5" t="n">
-        <v>5357</v>
+        <v>4766</v>
       </c>
       <c r="D5" t="n">
-        <v>3076</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>942</v>
+        <v>1036</v>
       </c>
       <c r="C6" t="n">
-        <v>3128</v>
+        <v>3486</v>
       </c>
       <c r="D6" t="n">
-        <v>1259</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>429</v>
+        <v>492</v>
       </c>
       <c r="C7" t="n">
-        <v>1789</v>
+        <v>2009</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="C8" t="n">
-        <v>858</v>
+        <v>906</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5735</v>
+        <v>6076</v>
       </c>
       <c r="C2" t="n">
-        <v>7623</v>
+        <v>8986</v>
       </c>
       <c r="D2" t="n">
-        <v>28075</v>
+        <v>25331</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3009</v>
+        <v>3560</v>
       </c>
       <c r="C3" t="n">
-        <v>7064</v>
+        <v>6732</v>
       </c>
       <c r="D3" t="n">
-        <v>18146</v>
+        <v>19129</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2311</v>
+        <v>2809</v>
       </c>
       <c r="C4" t="n">
-        <v>5970</v>
+        <v>4417</v>
       </c>
       <c r="D4" t="n">
-        <v>9479</v>
+        <v>9782</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1756</v>
+        <v>2084</v>
       </c>
       <c r="C5" t="n">
-        <v>5806</v>
+        <v>4609</v>
       </c>
       <c r="D5" t="n">
-        <v>3728</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1124</v>
+        <v>1273</v>
       </c>
       <c r="C6" t="n">
-        <v>4082</v>
+        <v>4017</v>
       </c>
       <c r="D6" t="n">
-        <v>1521</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>579</v>
+        <v>649</v>
       </c>
       <c r="C7" t="n">
-        <v>2348</v>
+        <v>2625</v>
       </c>
       <c r="D7" t="n">
-        <v>740</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="C8" t="n">
-        <v>1249</v>
+        <v>1370</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6649</v>
+        <v>8102</v>
       </c>
       <c r="C2" t="n">
-        <v>16087</v>
+        <v>14373</v>
       </c>
       <c r="D2" t="n">
-        <v>26239</v>
+        <v>26968</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3312</v>
+        <v>3709</v>
       </c>
       <c r="C3" t="n">
-        <v>6480</v>
+        <v>6782</v>
       </c>
       <c r="D3" t="n">
-        <v>18176</v>
+        <v>18648</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2208</v>
+        <v>2653</v>
       </c>
       <c r="C4" t="n">
-        <v>6250</v>
+        <v>5260</v>
       </c>
       <c r="D4" t="n">
-        <v>10347</v>
+        <v>10736</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1763</v>
+        <v>2132</v>
       </c>
       <c r="C5" t="n">
-        <v>5697</v>
+        <v>4389</v>
       </c>
       <c r="D5" t="n">
-        <v>4442</v>
+        <v>4432</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1263</v>
+        <v>1442</v>
       </c>
       <c r="C6" t="n">
-        <v>4741</v>
+        <v>4220</v>
       </c>
       <c r="D6" t="n">
-        <v>1782</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>706</v>
+        <v>795</v>
       </c>
       <c r="C7" t="n">
-        <v>3003</v>
+        <v>3143</v>
       </c>
       <c r="D7" t="n">
-        <v>839</v>
+        <v>801</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="C8" t="n">
-        <v>1656</v>
+        <v>1835</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C9" t="n">
-        <v>820</v>
+        <v>872</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D10" t="n">
         <v>251</v>
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6088</v>
+        <v>7343</v>
       </c>
       <c r="C2" t="n">
-        <v>11067</v>
+        <v>9888</v>
       </c>
       <c r="D2" t="n">
-        <v>21863</v>
+        <v>22469</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3941</v>
+        <v>4567</v>
       </c>
       <c r="C3" t="n">
-        <v>10662</v>
+        <v>10342</v>
       </c>
       <c r="D3" t="n">
-        <v>19755</v>
+        <v>20305</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1629</v>
+        <v>1969</v>
       </c>
       <c r="C4" t="n">
-        <v>8829</v>
+        <v>7041</v>
       </c>
       <c r="D4" t="n">
-        <v>9824</v>
+        <v>10071</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1167</v>
+        <v>1332</v>
       </c>
       <c r="C5" t="n">
-        <v>4646</v>
+        <v>4135</v>
       </c>
       <c r="D5" t="n">
-        <v>2940</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>652</v>
+        <v>734</v>
       </c>
       <c r="C6" t="n">
-        <v>2942</v>
+        <v>3080</v>
       </c>
       <c r="D6" t="n">
-        <v>822</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>1622</v>
+        <v>1798</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>803</v>
+        <v>854</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
         <v>245</v>
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>160</v>
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3794</v>
+        <v>4503</v>
       </c>
       <c r="C2" t="n">
-        <v>5834</v>
+        <v>4785</v>
       </c>
       <c r="D2" t="n">
-        <v>16072</v>
+        <v>15637</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4149</v>
+        <v>4898</v>
       </c>
       <c r="C3" t="n">
-        <v>9851</v>
+        <v>9217</v>
       </c>
       <c r="D3" t="n">
-        <v>19093</v>
+        <v>19624</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2162</v>
+        <v>2559</v>
       </c>
       <c r="C4" t="n">
-        <v>9726</v>
+        <v>8586</v>
       </c>
       <c r="D4" t="n">
-        <v>11049</v>
+        <v>11335</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1271</v>
+        <v>1473</v>
       </c>
       <c r="C5" t="n">
-        <v>6458</v>
+        <v>5419</v>
       </c>
       <c r="D5" t="n">
-        <v>3794</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>775</v>
+        <v>875</v>
       </c>
       <c r="C6" t="n">
-        <v>3665</v>
+        <v>3592</v>
       </c>
       <c r="D6" t="n">
-        <v>1019</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>2113</v>
+        <v>2295</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1046</v>
+        <v>1130</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3816</v>
+        <v>5014</v>
       </c>
       <c r="C2" t="n">
-        <v>5205</v>
+        <v>7477</v>
       </c>
       <c r="D2" t="n">
-        <v>23452</v>
+        <v>27941</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3395</v>
+        <v>3975</v>
       </c>
       <c r="C3" t="n">
-        <v>7108</v>
+        <v>6376</v>
       </c>
       <c r="D3" t="n">
-        <v>17399</v>
+        <v>17763</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2556</v>
+        <v>3062</v>
       </c>
       <c r="C4" t="n">
-        <v>9583</v>
+        <v>8710</v>
       </c>
       <c r="D4" t="n">
-        <v>12025</v>
+        <v>12343</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1463</v>
+        <v>1713</v>
       </c>
       <c r="C5" t="n">
-        <v>7891</v>
+        <v>6765</v>
       </c>
       <c r="D5" t="n">
-        <v>4793</v>
+        <v>4779</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>897</v>
+        <v>1026</v>
       </c>
       <c r="C6" t="n">
-        <v>4837</v>
+        <v>4399</v>
       </c>
       <c r="D6" t="n">
-        <v>1405</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="C7" t="n">
-        <v>2786</v>
+        <v>2863</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>1474</v>
+        <v>1597</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>648</v>
+        <v>671</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2277</v>
+        <v>2998</v>
       </c>
       <c r="C2" t="n">
-        <v>2505</v>
+        <v>3566</v>
       </c>
       <c r="D2" t="n">
-        <v>16395</v>
+        <v>19511</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3400</v>
+        <v>4103</v>
       </c>
       <c r="C3" t="n">
-        <v>6279</v>
+        <v>6553</v>
       </c>
       <c r="D3" t="n">
-        <v>17638</v>
+        <v>18423</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2808</v>
+        <v>3347</v>
       </c>
       <c r="C4" t="n">
-        <v>9611</v>
+        <v>8625</v>
       </c>
       <c r="D4" t="n">
-        <v>12746</v>
+        <v>13074</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1540</v>
+        <v>1790</v>
       </c>
       <c r="C5" t="n">
-        <v>9444</v>
+        <v>8292</v>
       </c>
       <c r="D5" t="n">
-        <v>5053</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>737</v>
+        <v>840</v>
       </c>
       <c r="C6" t="n">
-        <v>5639</v>
+        <v>5222</v>
       </c>
       <c r="D6" t="n">
-        <v>1368</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>2813</v>
+        <v>2947</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1068</v>
+        <v>1127</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2365</v>
+        <v>3155</v>
       </c>
       <c r="C2" t="n">
-        <v>5936</v>
+        <v>5238</v>
       </c>
       <c r="D2" t="n">
-        <v>21146</v>
+        <v>15065</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2524</v>
+        <v>3126</v>
       </c>
       <c r="C3" t="n">
-        <v>4116</v>
+        <v>4669</v>
       </c>
       <c r="D3" t="n">
-        <v>16321</v>
+        <v>17353</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2679</v>
+        <v>3181</v>
       </c>
       <c r="C4" t="n">
-        <v>7967</v>
+        <v>7573</v>
       </c>
       <c r="D4" t="n">
-        <v>13109</v>
+        <v>13498</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1809</v>
+        <v>2139</v>
       </c>
       <c r="C5" t="n">
-        <v>9410</v>
+        <v>8342</v>
       </c>
       <c r="D5" t="n">
-        <v>6007</v>
+        <v>6046</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>1087</v>
       </c>
       <c r="C6" t="n">
-        <v>7178</v>
+        <v>6465</v>
       </c>
       <c r="D6" t="n">
-        <v>1858</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>3947</v>
+        <v>3844</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1687</v>
+        <v>1790</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1655</v>
+        <v>2156</v>
       </c>
       <c r="C2" t="n">
-        <v>3542</v>
+        <v>2993</v>
       </c>
       <c r="D2" t="n">
-        <v>15030</v>
+        <v>10986</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2170</v>
+        <v>2749</v>
       </c>
       <c r="C3" t="n">
-        <v>4412</v>
+        <v>4446</v>
       </c>
       <c r="D3" t="n">
-        <v>15999</v>
+        <v>16180</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2426</v>
+        <v>2913</v>
       </c>
       <c r="C4" t="n">
-        <v>6475</v>
+        <v>6490</v>
       </c>
       <c r="D4" t="n">
-        <v>13237</v>
+        <v>13698</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1966</v>
+        <v>2308</v>
       </c>
       <c r="C5" t="n">
-        <v>9076</v>
+        <v>8223</v>
       </c>
       <c r="D5" t="n">
-        <v>6689</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1065</v>
+        <v>1267</v>
       </c>
       <c r="C6" t="n">
-        <v>8126</v>
+        <v>7280</v>
       </c>
       <c r="D6" t="n">
-        <v>2191</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="C7" t="n">
-        <v>4944</v>
+        <v>4659</v>
       </c>
       <c r="D7" t="n">
-        <v>749</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2176</v>
+        <v>2299</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3400,7 +3400,7 @@
         <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2431</v>
+        <v>4326</v>
       </c>
       <c r="C2" t="n">
-        <v>7663</v>
+        <v>9241</v>
       </c>
       <c r="D2" t="n">
-        <v>16070</v>
+        <v>15516</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1683</v>
+        <v>2143</v>
       </c>
       <c r="C3" t="n">
-        <v>3675</v>
+        <v>3462</v>
       </c>
       <c r="D3" t="n">
-        <v>14892</v>
+        <v>14676</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2034</v>
+        <v>2507</v>
       </c>
       <c r="C4" t="n">
-        <v>5508</v>
+        <v>5511</v>
       </c>
       <c r="D4" t="n">
-        <v>13078</v>
+        <v>13483</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1933</v>
+        <v>2287</v>
       </c>
       <c r="C5" t="n">
-        <v>7888</v>
+        <v>7369</v>
       </c>
       <c r="D5" t="n">
-        <v>7365</v>
+        <v>7491</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1263</v>
+        <v>1494</v>
       </c>
       <c r="C6" t="n">
-        <v>8407</v>
+        <v>7573</v>
       </c>
       <c r="D6" t="n">
-        <v>2724</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>510</v>
       </c>
       <c r="C7" t="n">
-        <v>6064</v>
+        <v>5607</v>
       </c>
       <c r="D7" t="n">
-        <v>910</v>
+        <v>889</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>3097</v>
+        <v>3130</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1090</v>
+        <v>1145</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4614</v>
+        <v>6624</v>
       </c>
       <c r="C2" t="n">
-        <v>8231</v>
+        <v>6295</v>
       </c>
       <c r="D2" t="n">
-        <v>16103</v>
+        <v>8054</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1776</v>
+        <v>3125</v>
       </c>
       <c r="C2" t="n">
-        <v>4475</v>
+        <v>5396</v>
       </c>
       <c r="D2" t="n">
-        <v>11956</v>
+        <v>11543</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2284</v>
+        <v>3004</v>
       </c>
       <c r="C3" t="n">
-        <v>4918</v>
+        <v>5020</v>
       </c>
       <c r="D3" t="n">
-        <v>16200</v>
+        <v>15863</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2825</v>
+        <v>3373</v>
       </c>
       <c r="C4" t="n">
-        <v>8126</v>
+        <v>7994</v>
       </c>
       <c r="D4" t="n">
-        <v>13318</v>
+        <v>13835</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1184</v>
+        <v>1422</v>
       </c>
       <c r="C5" t="n">
-        <v>11753</v>
+        <v>10680</v>
       </c>
       <c r="D5" t="n">
-        <v>6664</v>
+        <v>6743</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>403</v>
+        <v>471</v>
       </c>
       <c r="C6" t="n">
-        <v>7425</v>
+        <v>6904</v>
       </c>
       <c r="D6" t="n">
-        <v>2083</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>3035</v>
+        <v>3067</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1068</v>
+        <v>1122</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6384</v>
+        <v>6774</v>
       </c>
       <c r="C2" t="n">
-        <v>4625</v>
+        <v>8705</v>
       </c>
       <c r="D2" t="n">
-        <v>22864</v>
+        <v>20239</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1961</v>
+        <v>2814</v>
       </c>
       <c r="C3" t="n">
-        <v>4148</v>
+        <v>3172</v>
       </c>
       <c r="D3" t="n">
-        <v>3344</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4724</v>
+        <v>4923</v>
       </c>
       <c r="C2" t="n">
-        <v>5151</v>
+        <v>7382</v>
       </c>
       <c r="D2" t="n">
-        <v>20163</v>
+        <v>24408</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3423</v>
+        <v>3938</v>
       </c>
       <c r="C3" t="n">
-        <v>3810</v>
+        <v>5435</v>
       </c>
       <c r="D3" t="n">
-        <v>6377</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>886</v>
+        <v>1257</v>
       </c>
       <c r="C4" t="n">
-        <v>2475</v>
+        <v>1902</v>
       </c>
       <c r="D4" t="n">
-        <v>1855</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4595</v>
+        <v>4640</v>
       </c>
       <c r="C2" t="n">
-        <v>8986</v>
+        <v>7408</v>
       </c>
       <c r="D2" t="n">
-        <v>18699</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3339</v>
+        <v>3640</v>
       </c>
       <c r="C3" t="n">
-        <v>3930</v>
+        <v>5623</v>
       </c>
       <c r="D3" t="n">
-        <v>8123</v>
+        <v>7676</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1829</v>
+        <v>2211</v>
       </c>
       <c r="C4" t="n">
-        <v>3179</v>
+        <v>3863</v>
       </c>
       <c r="D4" t="n">
-        <v>2666</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>417</v>
+        <v>565</v>
       </c>
       <c r="C5" t="n">
-        <v>1451</v>
+        <v>1135</v>
       </c>
       <c r="D5" t="n">
-        <v>1269</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
         <v>174</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>76</v>
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5458</v>
+        <v>6524</v>
       </c>
       <c r="C2" t="n">
-        <v>8594</v>
+        <v>8808</v>
       </c>
       <c r="D2" t="n">
-        <v>25849</v>
+        <v>35528</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3235</v>
+        <v>3419</v>
       </c>
       <c r="C3" t="n">
-        <v>5685</v>
+        <v>5693</v>
       </c>
       <c r="D3" t="n">
-        <v>9158</v>
+        <v>9098</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2194</v>
+        <v>2462</v>
       </c>
       <c r="C4" t="n">
-        <v>3516</v>
+        <v>4728</v>
       </c>
       <c r="D4" t="n">
-        <v>3580</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>917</v>
+        <v>1140</v>
       </c>
       <c r="C5" t="n">
-        <v>2302</v>
+        <v>2525</v>
       </c>
       <c r="D5" t="n">
-        <v>1459</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="C6" t="n">
-        <v>884</v>
+        <v>712</v>
       </c>
       <c r="D6" t="n">
-        <v>957</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
         <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5689</v>
+        <v>7252</v>
       </c>
       <c r="C2" t="n">
-        <v>12797</v>
+        <v>7667</v>
       </c>
       <c r="D2" t="n">
-        <v>38623</v>
+        <v>36574</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3132</v>
+        <v>3571</v>
       </c>
       <c r="C3" t="n">
-        <v>5875</v>
+        <v>5946</v>
       </c>
       <c r="D3" t="n">
-        <v>10396</v>
+        <v>11735</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1674</v>
+        <v>1828</v>
       </c>
       <c r="C4" t="n">
-        <v>3859</v>
+        <v>4260</v>
       </c>
       <c r="D4" t="n">
-        <v>3914</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>812</v>
+        <v>933</v>
       </c>
       <c r="C5" t="n">
-        <v>2123</v>
+        <v>2679</v>
       </c>
       <c r="D5" t="n">
-        <v>1431</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>273</v>
+        <v>341</v>
       </c>
       <c r="C6" t="n">
         <v>1077</v>
       </c>
       <c r="D6" t="n">
-        <v>793</v>
+        <v>769</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>389</v>
+        <v>338</v>
       </c>
       <c r="D7" t="n">
         <v>514</v>
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4657</v>
+        <v>5725</v>
       </c>
       <c r="C2" t="n">
-        <v>7628</v>
+        <v>3951</v>
       </c>
       <c r="D2" t="n">
-        <v>34224</v>
+        <v>40471</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3647</v>
+        <v>4477</v>
       </c>
       <c r="C3" t="n">
-        <v>8536</v>
+        <v>5971</v>
       </c>
       <c r="D3" t="n">
-        <v>14372</v>
+        <v>15044</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2086</v>
+        <v>2360</v>
       </c>
       <c r="C4" t="n">
-        <v>4998</v>
+        <v>5134</v>
       </c>
       <c r="D4" t="n">
-        <v>5064</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1110</v>
+        <v>1218</v>
       </c>
       <c r="C5" t="n">
-        <v>3095</v>
+        <v>3549</v>
       </c>
       <c r="D5" t="n">
-        <v>1888</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>589</v>
       </c>
       <c r="C6" t="n">
-        <v>1656</v>
+        <v>1971</v>
       </c>
       <c r="D6" t="n">
-        <v>904</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>773</v>
+        <v>750</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>81</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3721</v>
+        <v>4833</v>
       </c>
       <c r="C2" t="n">
-        <v>5380</v>
+        <v>5750</v>
       </c>
       <c r="D2" t="n">
-        <v>34326</v>
+        <v>33173</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3404</v>
+        <v>4181</v>
       </c>
       <c r="C3" t="n">
-        <v>6981</v>
+        <v>4240</v>
       </c>
       <c r="D3" t="n">
-        <v>16513</v>
+        <v>18173</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2433</v>
+        <v>2916</v>
       </c>
       <c r="C4" t="n">
-        <v>6864</v>
+        <v>5493</v>
       </c>
       <c r="D4" t="n">
-        <v>6697</v>
+        <v>6723</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1399</v>
+        <v>1543</v>
       </c>
       <c r="C5" t="n">
-        <v>4023</v>
+        <v>4327</v>
       </c>
       <c r="D5" t="n">
-        <v>2409</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>720</v>
+        <v>816</v>
       </c>
       <c r="C6" t="n">
-        <v>2396</v>
+        <v>2766</v>
       </c>
       <c r="D6" t="n">
-        <v>1052</v>
+        <v>978</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>1231</v>
+        <v>1364</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>28</v>

--- a/output/yearly_population_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_55_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5223</v>
+        <v>6317</v>
       </c>
       <c r="C2" t="n">
-        <v>11875</v>
+        <v>10374</v>
       </c>
       <c r="D2" t="n">
-        <v>29230</v>
+        <v>38882</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3696</v>
+        <v>4238</v>
       </c>
       <c r="C3" t="n">
-        <v>4351</v>
+        <v>7017</v>
       </c>
       <c r="D3" t="n">
-        <v>19082</v>
+        <v>20203</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2983</v>
+        <v>3290</v>
       </c>
       <c r="C4" t="n">
-        <v>4741</v>
+        <v>5491</v>
       </c>
       <c r="D4" t="n">
-        <v>8497</v>
+        <v>8365</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1909</v>
+        <v>2027</v>
       </c>
       <c r="C5" t="n">
-        <v>4766</v>
+        <v>3630</v>
       </c>
       <c r="D5" t="n">
-        <v>2890</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1036</v>
+        <v>1118</v>
       </c>
       <c r="C6" t="n">
-        <v>3486</v>
+        <v>2666</v>
       </c>
       <c r="D6" t="n">
-        <v>1172</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>560</v>
       </c>
       <c r="C7" t="n">
-        <v>2009</v>
+        <v>1551</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C8" t="n">
-        <v>906</v>
+        <v>712</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
         <v>246</v>
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6076</v>
+        <v>7779</v>
       </c>
       <c r="C2" t="n">
-        <v>8986</v>
+        <v>14268</v>
       </c>
       <c r="D2" t="n">
-        <v>25331</v>
+        <v>36141</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3560</v>
+        <v>4202</v>
       </c>
       <c r="C3" t="n">
-        <v>6732</v>
+        <v>7502</v>
       </c>
       <c r="D3" t="n">
-        <v>19129</v>
+        <v>21385</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2809</v>
+        <v>3162</v>
       </c>
       <c r="C4" t="n">
-        <v>4417</v>
+        <v>6041</v>
       </c>
       <c r="D4" t="n">
-        <v>9782</v>
+        <v>10042</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2084</v>
+        <v>2263</v>
       </c>
       <c r="C5" t="n">
-        <v>4609</v>
+        <v>4412</v>
       </c>
       <c r="D5" t="n">
-        <v>3663</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1273</v>
+        <v>1381</v>
       </c>
       <c r="C6" t="n">
-        <v>4017</v>
+        <v>3039</v>
       </c>
       <c r="D6" t="n">
-        <v>1392</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>649</v>
+        <v>713</v>
       </c>
       <c r="C7" t="n">
-        <v>2625</v>
+        <v>2026</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="C8" t="n">
-        <v>1370</v>
+        <v>1073</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>474</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
         <v>163</v>
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8102</v>
+        <v>9871</v>
       </c>
       <c r="C2" t="n">
-        <v>14373</v>
+        <v>9798</v>
       </c>
       <c r="D2" t="n">
-        <v>26968</v>
+        <v>33616</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3709</v>
+        <v>4558</v>
       </c>
       <c r="C3" t="n">
-        <v>6782</v>
+        <v>9097</v>
       </c>
       <c r="D3" t="n">
-        <v>18648</v>
+        <v>21787</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2653</v>
+        <v>3048</v>
       </c>
       <c r="C4" t="n">
-        <v>5260</v>
+        <v>6546</v>
       </c>
       <c r="D4" t="n">
-        <v>10736</v>
+        <v>11273</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2132</v>
+        <v>2329</v>
       </c>
       <c r="C5" t="n">
-        <v>4389</v>
+        <v>4950</v>
       </c>
       <c r="D5" t="n">
-        <v>4432</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1442</v>
+        <v>1574</v>
       </c>
       <c r="C6" t="n">
-        <v>4220</v>
+        <v>3536</v>
       </c>
       <c r="D6" t="n">
-        <v>1665</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>795</v>
+        <v>875</v>
       </c>
       <c r="C7" t="n">
-        <v>3143</v>
+        <v>2432</v>
       </c>
       <c r="D7" t="n">
-        <v>801</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>366</v>
+        <v>417</v>
       </c>
       <c r="C8" t="n">
-        <v>1835</v>
+        <v>1426</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C9" t="n">
-        <v>872</v>
+        <v>692</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>375</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7343</v>
+        <v>8917</v>
       </c>
       <c r="C2" t="n">
-        <v>9888</v>
+        <v>6741</v>
       </c>
       <c r="D2" t="n">
-        <v>22469</v>
+        <v>27938</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4567</v>
+        <v>5470</v>
       </c>
       <c r="C3" t="n">
-        <v>10342</v>
+        <v>12532</v>
       </c>
       <c r="D3" t="n">
-        <v>20305</v>
+        <v>23332</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1969</v>
+        <v>2151</v>
       </c>
       <c r="C4" t="n">
-        <v>7041</v>
+        <v>8333</v>
       </c>
       <c r="D4" t="n">
-        <v>10071</v>
+        <v>10393</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1332</v>
+        <v>1454</v>
       </c>
       <c r="C5" t="n">
-        <v>4135</v>
+        <v>3465</v>
       </c>
       <c r="D5" t="n">
-        <v>2823</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>734</v>
+        <v>808</v>
       </c>
       <c r="C6" t="n">
-        <v>3080</v>
+        <v>2383</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>1798</v>
+        <v>1397</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>854</v>
+        <v>678</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4503</v>
+        <v>5369</v>
       </c>
       <c r="C2" t="n">
-        <v>4785</v>
+        <v>3245</v>
       </c>
       <c r="D2" t="n">
-        <v>15637</v>
+        <v>19747</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4898</v>
+        <v>5929</v>
       </c>
       <c r="C3" t="n">
-        <v>9217</v>
+        <v>9006</v>
       </c>
       <c r="D3" t="n">
-        <v>19624</v>
+        <v>22838</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2559</v>
+        <v>2977</v>
       </c>
       <c r="C4" t="n">
-        <v>8586</v>
+        <v>10414</v>
       </c>
       <c r="D4" t="n">
-        <v>11335</v>
+        <v>12040</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1473</v>
+        <v>1608</v>
       </c>
       <c r="C5" t="n">
-        <v>5419</v>
+        <v>5522</v>
       </c>
       <c r="D5" t="n">
-        <v>3723</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="6">
@@ -2080,10 +2080,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>875</v>
+        <v>963</v>
       </c>
       <c r="C6" t="n">
-        <v>3592</v>
+        <v>2869</v>
       </c>
       <c r="D6" t="n">
         <v>973</v>
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="C7" t="n">
-        <v>2295</v>
+        <v>1780</v>
       </c>
       <c r="D7" t="n">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>1130</v>
+        <v>888</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
         <v>210</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5014</v>
+        <v>4807</v>
       </c>
       <c r="C2" t="n">
-        <v>7477</v>
+        <v>7956</v>
       </c>
       <c r="D2" t="n">
-        <v>27941</v>
+        <v>18411</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3975</v>
+        <v>4784</v>
       </c>
       <c r="C3" t="n">
-        <v>6376</v>
+        <v>5646</v>
       </c>
       <c r="D3" t="n">
-        <v>17763</v>
+        <v>20882</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3062</v>
+        <v>3643</v>
       </c>
       <c r="C4" t="n">
-        <v>8710</v>
+        <v>9521</v>
       </c>
       <c r="D4" t="n">
-        <v>12343</v>
+        <v>13436</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1713</v>
+        <v>1929</v>
       </c>
       <c r="C5" t="n">
-        <v>6765</v>
+        <v>7661</v>
       </c>
       <c r="D5" t="n">
-        <v>4779</v>
+        <v>4863</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1026</v>
+        <v>1125</v>
       </c>
       <c r="C6" t="n">
-        <v>4399</v>
+        <v>4041</v>
       </c>
       <c r="D6" t="n">
-        <v>1356</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>468</v>
+        <v>524</v>
       </c>
       <c r="C7" t="n">
-        <v>2863</v>
+        <v>2255</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C8" t="n">
-        <v>1597</v>
+        <v>1246</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>671</v>
+        <v>558</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2998</v>
+        <v>2906</v>
       </c>
       <c r="C2" t="n">
-        <v>3566</v>
+        <v>3773</v>
       </c>
       <c r="D2" t="n">
-        <v>19511</v>
+        <v>12914</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4103</v>
+        <v>4622</v>
       </c>
       <c r="C3" t="n">
-        <v>6553</v>
+        <v>6241</v>
       </c>
       <c r="D3" t="n">
-        <v>18423</v>
+        <v>20157</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3347</v>
+        <v>4008</v>
       </c>
       <c r="C4" t="n">
-        <v>8625</v>
+        <v>9009</v>
       </c>
       <c r="D4" t="n">
-        <v>13074</v>
+        <v>14362</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1790</v>
+        <v>2000</v>
       </c>
       <c r="C5" t="n">
-        <v>8292</v>
+        <v>9257</v>
       </c>
       <c r="D5" t="n">
-        <v>5043</v>
+        <v>5154</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>840</v>
+        <v>931</v>
       </c>
       <c r="C6" t="n">
-        <v>5222</v>
+        <v>4706</v>
       </c>
       <c r="D6" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C7" t="n">
-        <v>2947</v>
+        <v>2335</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>913</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
         <v>285</v>
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3155</v>
+        <v>3482</v>
       </c>
       <c r="C2" t="n">
-        <v>5238</v>
+        <v>4237</v>
       </c>
       <c r="D2" t="n">
-        <v>15065</v>
+        <v>14902</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3126</v>
+        <v>3371</v>
       </c>
       <c r="C3" t="n">
-        <v>4669</v>
+        <v>4594</v>
       </c>
       <c r="D3" t="n">
-        <v>17353</v>
+        <v>17907</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3181</v>
+        <v>3716</v>
       </c>
       <c r="C4" t="n">
-        <v>7573</v>
+        <v>7632</v>
       </c>
       <c r="D4" t="n">
-        <v>13498</v>
+        <v>14815</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2139</v>
+        <v>2470</v>
       </c>
       <c r="C5" t="n">
-        <v>8342</v>
+        <v>9046</v>
       </c>
       <c r="D5" t="n">
-        <v>6046</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1087</v>
+        <v>1209</v>
       </c>
       <c r="C6" t="n">
-        <v>6465</v>
+        <v>6545</v>
       </c>
       <c r="D6" t="n">
-        <v>1816</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="C7" t="n">
-        <v>3844</v>
+        <v>3263</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1790</v>
+        <v>1432</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>554</v>
+        <v>475</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2156</v>
+        <v>2555</v>
       </c>
       <c r="C2" t="n">
-        <v>2993</v>
+        <v>2979</v>
       </c>
       <c r="D2" t="n">
-        <v>10986</v>
+        <v>10808</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2749</v>
+        <v>2986</v>
       </c>
       <c r="C3" t="n">
-        <v>4446</v>
+        <v>4059</v>
       </c>
       <c r="D3" t="n">
-        <v>16180</v>
+        <v>16624</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2913</v>
+        <v>3334</v>
       </c>
       <c r="C4" t="n">
-        <v>6490</v>
+        <v>6497</v>
       </c>
       <c r="D4" t="n">
-        <v>13698</v>
+        <v>14892</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2308</v>
+        <v>2673</v>
       </c>
       <c r="C5" t="n">
-        <v>8223</v>
+        <v>8716</v>
       </c>
       <c r="D5" t="n">
-        <v>6765</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1267</v>
+        <v>1419</v>
       </c>
       <c r="C6" t="n">
-        <v>7280</v>
+        <v>7544</v>
       </c>
       <c r="D6" t="n">
-        <v>2155</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>4659</v>
+        <v>4193</v>
       </c>
       <c r="D7" t="n">
-        <v>729</v>
+        <v>736</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2299</v>
+        <v>1868</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>610</v>
+        <v>526</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4326</v>
+        <v>3397</v>
       </c>
       <c r="C2" t="n">
-        <v>9241</v>
+        <v>8765</v>
       </c>
       <c r="D2" t="n">
-        <v>15516</v>
+        <v>13228</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2143</v>
+        <v>2389</v>
       </c>
       <c r="C3" t="n">
-        <v>3462</v>
+        <v>3245</v>
       </c>
       <c r="D3" t="n">
-        <v>14676</v>
+        <v>15021</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2507</v>
+        <v>2822</v>
       </c>
       <c r="C4" t="n">
-        <v>5511</v>
+        <v>5355</v>
       </c>
       <c r="D4" t="n">
-        <v>13483</v>
+        <v>14529</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2287</v>
+        <v>2637</v>
       </c>
       <c r="C5" t="n">
-        <v>7369</v>
+        <v>7661</v>
       </c>
       <c r="D5" t="n">
-        <v>7491</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1494</v>
+        <v>1698</v>
       </c>
       <c r="C6" t="n">
-        <v>7573</v>
+        <v>7920</v>
       </c>
       <c r="D6" t="n">
-        <v>2702</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>510</v>
+        <v>571</v>
       </c>
       <c r="C7" t="n">
-        <v>5607</v>
+        <v>5447</v>
       </c>
       <c r="D7" t="n">
-        <v>889</v>
+        <v>899</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>3130</v>
+        <v>2641</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>1145</v>
+        <v>951</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6624</v>
+        <v>7631</v>
       </c>
       <c r="C2" t="n">
-        <v>6295</v>
+        <v>4144</v>
       </c>
       <c r="D2" t="n">
-        <v>8054</v>
+        <v>5714</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3125</v>
+        <v>2460</v>
       </c>
       <c r="C2" t="n">
-        <v>5396</v>
+        <v>5118</v>
       </c>
       <c r="D2" t="n">
-        <v>11543</v>
+        <v>9841</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3004</v>
+        <v>3244</v>
       </c>
       <c r="C3" t="n">
-        <v>5020</v>
+        <v>4728</v>
       </c>
       <c r="D3" t="n">
-        <v>15863</v>
+        <v>16137</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3373</v>
+        <v>3854</v>
       </c>
       <c r="C4" t="n">
-        <v>7994</v>
+        <v>7921</v>
       </c>
       <c r="D4" t="n">
-        <v>13835</v>
+        <v>14884</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1422</v>
+        <v>1617</v>
       </c>
       <c r="C5" t="n">
-        <v>10680</v>
+        <v>11140</v>
       </c>
       <c r="D5" t="n">
-        <v>6743</v>
+        <v>7128</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>471</v>
+        <v>527</v>
       </c>
       <c r="C6" t="n">
-        <v>6904</v>
+        <v>6812</v>
       </c>
       <c r="D6" t="n">
-        <v>2055</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>3067</v>
+        <v>2588</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>1122</v>
+        <v>931</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6774</v>
+        <v>7206</v>
       </c>
       <c r="C2" t="n">
-        <v>8705</v>
+        <v>5943</v>
       </c>
       <c r="D2" t="n">
-        <v>20239</v>
+        <v>14749</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2814</v>
+        <v>3241</v>
       </c>
       <c r="C3" t="n">
-        <v>3172</v>
+        <v>2121</v>
       </c>
       <c r="D3" t="n">
-        <v>1992</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4923</v>
+        <v>5104</v>
       </c>
       <c r="C2" t="n">
-        <v>7382</v>
+        <v>6755</v>
       </c>
       <c r="D2" t="n">
-        <v>24408</v>
+        <v>23683</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3938</v>
+        <v>4293</v>
       </c>
       <c r="C3" t="n">
-        <v>5435</v>
+        <v>3741</v>
       </c>
       <c r="D3" t="n">
-        <v>4910</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1257</v>
+        <v>1441</v>
       </c>
       <c r="C4" t="n">
-        <v>1902</v>
+        <v>1285</v>
       </c>
       <c r="D4" t="n">
-        <v>1582</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4640</v>
+        <v>4937</v>
       </c>
       <c r="C2" t="n">
-        <v>7408</v>
+        <v>5470</v>
       </c>
       <c r="D2" t="n">
-        <v>20587</v>
+        <v>25515</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3640</v>
+        <v>3866</v>
       </c>
       <c r="C3" t="n">
-        <v>5623</v>
+        <v>4660</v>
       </c>
       <c r="D3" t="n">
-        <v>7676</v>
+        <v>6623</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2211</v>
+        <v>2430</v>
       </c>
       <c r="C4" t="n">
-        <v>3863</v>
+        <v>2649</v>
       </c>
       <c r="D4" t="n">
-        <v>2172</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>565</v>
+        <v>651</v>
       </c>
       <c r="C5" t="n">
-        <v>1135</v>
+        <v>796</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6524</v>
+        <v>5888</v>
       </c>
       <c r="C2" t="n">
-        <v>8808</v>
+        <v>6177</v>
       </c>
       <c r="D2" t="n">
-        <v>35528</v>
+        <v>33652</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3419</v>
+        <v>3602</v>
       </c>
       <c r="C3" t="n">
-        <v>5693</v>
+        <v>4418</v>
       </c>
       <c r="D3" t="n">
-        <v>9098</v>
+        <v>9028</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2462</v>
+        <v>2686</v>
       </c>
       <c r="C4" t="n">
-        <v>4728</v>
+        <v>3649</v>
       </c>
       <c r="D4" t="n">
-        <v>3109</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1140</v>
+        <v>1268</v>
       </c>
       <c r="C5" t="n">
-        <v>2525</v>
+        <v>1757</v>
       </c>
       <c r="D5" t="n">
-        <v>1335</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="C6" t="n">
-        <v>712</v>
+        <v>550</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7252</v>
+        <v>8334</v>
       </c>
       <c r="C2" t="n">
-        <v>7667</v>
+        <v>5918</v>
       </c>
       <c r="D2" t="n">
-        <v>36574</v>
+        <v>40970</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>3422</v>
       </c>
       <c r="C3" t="n">
-        <v>5946</v>
+        <v>4355</v>
       </c>
       <c r="D3" t="n">
-        <v>11735</v>
+        <v>11416</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1828</v>
+        <v>1940</v>
       </c>
       <c r="C4" t="n">
-        <v>4260</v>
+        <v>3308</v>
       </c>
       <c r="D4" t="n">
-        <v>3583</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>933</v>
+        <v>1034</v>
       </c>
       <c r="C5" t="n">
-        <v>2679</v>
+        <v>2017</v>
       </c>
       <c r="D5" t="n">
-        <v>1286</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="C6" t="n">
-        <v>1077</v>
+        <v>780</v>
       </c>
       <c r="D6" t="n">
-        <v>769</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>338</v>
+        <v>284</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5725</v>
+        <v>6650</v>
       </c>
       <c r="C2" t="n">
-        <v>3951</v>
+        <v>10766</v>
       </c>
       <c r="D2" t="n">
-        <v>40471</v>
+        <v>37359</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4477</v>
+        <v>4903</v>
       </c>
       <c r="C3" t="n">
-        <v>5971</v>
+        <v>4576</v>
       </c>
       <c r="D3" t="n">
-        <v>15044</v>
+        <v>15540</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2360</v>
+        <v>2355</v>
       </c>
       <c r="C4" t="n">
-        <v>5134</v>
+        <v>3840</v>
       </c>
       <c r="D4" t="n">
-        <v>5117</v>
+        <v>4773</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1218</v>
+        <v>1320</v>
       </c>
       <c r="C5" t="n">
-        <v>3549</v>
+        <v>2743</v>
       </c>
       <c r="D5" t="n">
-        <v>1675</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>589</v>
+        <v>662</v>
       </c>
       <c r="C6" t="n">
-        <v>1971</v>
+        <v>1482</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C7" t="n">
-        <v>750</v>
+        <v>565</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4833</v>
+        <v>5609</v>
       </c>
       <c r="C2" t="n">
-        <v>5750</v>
+        <v>9209</v>
       </c>
       <c r="D2" t="n">
-        <v>33173</v>
+        <v>42386</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4181</v>
+        <v>4737</v>
       </c>
       <c r="C3" t="n">
-        <v>4240</v>
+        <v>6882</v>
       </c>
       <c r="D3" t="n">
-        <v>18173</v>
+        <v>17912</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2916</v>
+        <v>3090</v>
       </c>
       <c r="C4" t="n">
-        <v>5493</v>
+        <v>4176</v>
       </c>
       <c r="D4" t="n">
-        <v>6723</v>
+        <v>6695</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1543</v>
+        <v>1621</v>
       </c>
       <c r="C5" t="n">
-        <v>4327</v>
+        <v>3286</v>
       </c>
       <c r="D5" t="n">
-        <v>2251</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>816</v>
+        <v>897</v>
       </c>
       <c r="C6" t="n">
-        <v>2766</v>
+        <v>2116</v>
       </c>
       <c r="D6" t="n">
-        <v>978</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>392</v>
       </c>
       <c r="C7" t="n">
-        <v>1364</v>
+        <v>1050</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>517</v>
+        <v>413</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_55_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6317</v>
+        <v>797</v>
       </c>
       <c r="C2" t="n">
-        <v>10374</v>
+        <v>2688</v>
       </c>
       <c r="D2" t="n">
-        <v>38882</v>
+        <v>19949</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4238</v>
+        <v>1285</v>
       </c>
       <c r="C3" t="n">
-        <v>7017</v>
+        <v>6444</v>
       </c>
       <c r="D3" t="n">
-        <v>20203</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3290</v>
+        <v>828</v>
       </c>
       <c r="C4" t="n">
-        <v>5491</v>
+        <v>6153</v>
       </c>
       <c r="D4" t="n">
-        <v>8365</v>
+        <v>7201</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2027</v>
+        <v>428</v>
       </c>
       <c r="C5" t="n">
-        <v>3630</v>
+        <v>3252</v>
       </c>
       <c r="D5" t="n">
-        <v>2829</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1118</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>2666</v>
+        <v>1375</v>
       </c>
       <c r="D6" t="n">
-        <v>1116</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>560</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1551</v>
+        <v>603</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>214</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>712</v>
+        <v>344</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7779</v>
+        <v>1128</v>
       </c>
       <c r="C2" t="n">
-        <v>14268</v>
+        <v>5789</v>
       </c>
       <c r="D2" t="n">
-        <v>36141</v>
+        <v>23717</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4202</v>
+        <v>881</v>
       </c>
       <c r="C3" t="n">
-        <v>7502</v>
+        <v>3805</v>
       </c>
       <c r="D3" t="n">
-        <v>21385</v>
+        <v>16094</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3162</v>
+        <v>913</v>
       </c>
       <c r="C4" t="n">
-        <v>6041</v>
+        <v>6248</v>
       </c>
       <c r="D4" t="n">
-        <v>10042</v>
+        <v>8825</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2263</v>
+        <v>550</v>
       </c>
       <c r="C5" t="n">
-        <v>4412</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="n">
-        <v>3566</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1381</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>3039</v>
+        <v>2328</v>
       </c>
       <c r="D6" t="n">
-        <v>1364</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>713</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>2026</v>
+        <v>986</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1073</v>
+        <v>466</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9871</v>
+        <v>580</v>
       </c>
       <c r="C2" t="n">
-        <v>9798</v>
+        <v>2364</v>
       </c>
       <c r="D2" t="n">
-        <v>33616</v>
+        <v>15994</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4558</v>
+        <v>925</v>
       </c>
       <c r="C3" t="n">
-        <v>9097</v>
+        <v>4434</v>
       </c>
       <c r="D3" t="n">
-        <v>21787</v>
+        <v>16631</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3048</v>
+        <v>999</v>
       </c>
       <c r="C4" t="n">
-        <v>6546</v>
+        <v>5732</v>
       </c>
       <c r="D4" t="n">
-        <v>11273</v>
+        <v>9817</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2329</v>
+        <v>564</v>
       </c>
       <c r="C5" t="n">
-        <v>4950</v>
+        <v>5787</v>
       </c>
       <c r="D5" t="n">
-        <v>4390</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1574</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>3536</v>
+        <v>3128</v>
       </c>
       <c r="D6" t="n">
-        <v>1628</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>875</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2432</v>
+        <v>998</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>417</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1426</v>
+        <v>487</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>164</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>692</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8917</v>
+        <v>553</v>
       </c>
       <c r="C2" t="n">
-        <v>6741</v>
+        <v>6234</v>
       </c>
       <c r="D2" t="n">
-        <v>27938</v>
+        <v>21597</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5470</v>
+        <v>651</v>
       </c>
       <c r="C3" t="n">
-        <v>12532</v>
+        <v>2908</v>
       </c>
       <c r="D3" t="n">
-        <v>23332</v>
+        <v>15363</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2151</v>
+        <v>856</v>
       </c>
       <c r="C4" t="n">
-        <v>8333</v>
+        <v>4957</v>
       </c>
       <c r="D4" t="n">
-        <v>10393</v>
+        <v>10761</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1454</v>
+        <v>677</v>
       </c>
       <c r="C5" t="n">
-        <v>3465</v>
+        <v>5749</v>
       </c>
       <c r="D5" t="n">
-        <v>2775</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>808</v>
+        <v>346</v>
       </c>
       <c r="C6" t="n">
-        <v>2383</v>
+        <v>4402</v>
       </c>
       <c r="D6" t="n">
-        <v>768</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>1397</v>
+        <v>1998</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>678</v>
+        <v>716</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5369</v>
+        <v>295</v>
       </c>
       <c r="C2" t="n">
-        <v>3245</v>
+        <v>3364</v>
       </c>
       <c r="D2" t="n">
-        <v>19747</v>
+        <v>15507</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5929</v>
+        <v>535</v>
       </c>
       <c r="C3" t="n">
-        <v>9006</v>
+        <v>3989</v>
       </c>
       <c r="D3" t="n">
-        <v>22838</v>
+        <v>15325</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2977</v>
+        <v>723</v>
       </c>
       <c r="C4" t="n">
-        <v>10414</v>
+        <v>4013</v>
       </c>
       <c r="D4" t="n">
-        <v>12040</v>
+        <v>11244</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1608</v>
+        <v>718</v>
       </c>
       <c r="C5" t="n">
-        <v>5522</v>
+        <v>5508</v>
       </c>
       <c r="D5" t="n">
-        <v>3694</v>
+        <v>5285</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>963</v>
+        <v>422</v>
       </c>
       <c r="C6" t="n">
-        <v>2869</v>
+        <v>5129</v>
       </c>
       <c r="D6" t="n">
-        <v>973</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>1780</v>
+        <v>2864</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>888</v>
+        <v>1055</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>446</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4807</v>
+        <v>562</v>
       </c>
       <c r="C2" t="n">
-        <v>7956</v>
+        <v>10270</v>
       </c>
       <c r="D2" t="n">
-        <v>18411</v>
+        <v>24237</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4784</v>
+        <v>365</v>
       </c>
       <c r="C3" t="n">
-        <v>5646</v>
+        <v>3237</v>
       </c>
       <c r="D3" t="n">
-        <v>20882</v>
+        <v>14443</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3643</v>
+        <v>561</v>
       </c>
       <c r="C4" t="n">
-        <v>9521</v>
+        <v>3917</v>
       </c>
       <c r="D4" t="n">
-        <v>13436</v>
+        <v>11460</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1929</v>
+        <v>664</v>
       </c>
       <c r="C5" t="n">
-        <v>7661</v>
+        <v>4728</v>
       </c>
       <c r="D5" t="n">
-        <v>4863</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1125</v>
+        <v>502</v>
       </c>
       <c r="C6" t="n">
-        <v>4041</v>
+        <v>5249</v>
       </c>
       <c r="D6" t="n">
-        <v>1351</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>524</v>
+        <v>223</v>
       </c>
       <c r="C7" t="n">
-        <v>2255</v>
+        <v>3889</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1246</v>
+        <v>1809</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>558</v>
+        <v>682</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2906</v>
+        <v>373</v>
       </c>
       <c r="C2" t="n">
-        <v>3773</v>
+        <v>5258</v>
       </c>
       <c r="D2" t="n">
-        <v>12914</v>
+        <v>17451</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4622</v>
+        <v>540</v>
       </c>
       <c r="C3" t="n">
-        <v>6241</v>
+        <v>5505</v>
       </c>
       <c r="D3" t="n">
-        <v>20157</v>
+        <v>16215</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4008</v>
+        <v>889</v>
       </c>
       <c r="C4" t="n">
-        <v>9009</v>
+        <v>5499</v>
       </c>
       <c r="D4" t="n">
-        <v>14362</v>
+        <v>11877</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2000</v>
+        <v>512</v>
       </c>
       <c r="C5" t="n">
-        <v>9257</v>
+        <v>7165</v>
       </c>
       <c r="D5" t="n">
-        <v>5154</v>
+        <v>5617</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>931</v>
+        <v>206</v>
       </c>
       <c r="C6" t="n">
-        <v>4706</v>
+        <v>5148</v>
       </c>
       <c r="D6" t="n">
-        <v>1318</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>2335</v>
+        <v>1772</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>913</v>
+        <v>668</v>
       </c>
       <c r="D8" t="n">
         <v>377</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3482</v>
+        <v>267</v>
       </c>
       <c r="C2" t="n">
-        <v>4237</v>
+        <v>2690</v>
       </c>
       <c r="D2" t="n">
-        <v>14902</v>
+        <v>13383</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3371</v>
+        <v>398</v>
       </c>
       <c r="C3" t="n">
-        <v>4594</v>
+        <v>4783</v>
       </c>
       <c r="D3" t="n">
-        <v>17907</v>
+        <v>15230</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3716</v>
+        <v>606</v>
       </c>
       <c r="C4" t="n">
-        <v>7632</v>
+        <v>5174</v>
       </c>
       <c r="D4" t="n">
-        <v>14815</v>
+        <v>11751</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2470</v>
+        <v>479</v>
       </c>
       <c r="C5" t="n">
-        <v>9046</v>
+        <v>5652</v>
       </c>
       <c r="D5" t="n">
-        <v>6323</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1209</v>
+        <v>195</v>
       </c>
       <c r="C6" t="n">
-        <v>6545</v>
+        <v>4954</v>
       </c>
       <c r="D6" t="n">
-        <v>1829</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>346</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>3263</v>
+        <v>2356</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1432</v>
+        <v>724</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>475</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2555</v>
+        <v>333</v>
       </c>
       <c r="C2" t="n">
-        <v>2979</v>
+        <v>6957</v>
       </c>
       <c r="D2" t="n">
-        <v>10808</v>
+        <v>14458</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2986</v>
+        <v>280</v>
       </c>
       <c r="C3" t="n">
-        <v>4059</v>
+        <v>3198</v>
       </c>
       <c r="D3" t="n">
-        <v>16624</v>
+        <v>13837</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3334</v>
+        <v>446</v>
       </c>
       <c r="C4" t="n">
-        <v>6497</v>
+        <v>4848</v>
       </c>
       <c r="D4" t="n">
-        <v>14892</v>
+        <v>12061</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2673</v>
+        <v>484</v>
       </c>
       <c r="C5" t="n">
-        <v>8716</v>
+        <v>5277</v>
       </c>
       <c r="D5" t="n">
-        <v>7148</v>
+        <v>6727</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1419</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>7544</v>
+        <v>5308</v>
       </c>
       <c r="D6" t="n">
-        <v>2188</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>310</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>4193</v>
+        <v>3676</v>
       </c>
       <c r="D7" t="n">
-        <v>736</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1868</v>
+        <v>1498</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>526</v>
+        <v>476</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3397</v>
+        <v>249</v>
       </c>
       <c r="C2" t="n">
-        <v>8765</v>
+        <v>6463</v>
       </c>
       <c r="D2" t="n">
-        <v>13228</v>
+        <v>19358</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2389</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>3245</v>
+        <v>4417</v>
       </c>
       <c r="D3" t="n">
-        <v>15021</v>
+        <v>12974</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2822</v>
+        <v>321</v>
       </c>
       <c r="C4" t="n">
-        <v>5355</v>
+        <v>3891</v>
       </c>
       <c r="D4" t="n">
-        <v>14529</v>
+        <v>11885</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2637</v>
+        <v>427</v>
       </c>
       <c r="C5" t="n">
-        <v>7661</v>
+        <v>4953</v>
       </c>
       <c r="D5" t="n">
-        <v>7971</v>
+        <v>7444</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1698</v>
+        <v>351</v>
       </c>
       <c r="C6" t="n">
-        <v>7920</v>
+        <v>5237</v>
       </c>
       <c r="D6" t="n">
-        <v>2779</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>571</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>5447</v>
+        <v>4442</v>
       </c>
       <c r="D7" t="n">
-        <v>899</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2641</v>
+        <v>2479</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>951</v>
+        <v>916</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7631</v>
+        <v>2179</v>
       </c>
       <c r="C2" t="n">
-        <v>4144</v>
+        <v>7182</v>
       </c>
       <c r="D2" t="n">
-        <v>5714</v>
+        <v>15675</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2460</v>
+        <v>246</v>
       </c>
       <c r="C2" t="n">
-        <v>5118</v>
+        <v>7616</v>
       </c>
       <c r="D2" t="n">
-        <v>9841</v>
+        <v>30101</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3244</v>
+        <v>211</v>
       </c>
       <c r="C3" t="n">
-        <v>4728</v>
+        <v>4696</v>
       </c>
       <c r="D3" t="n">
-        <v>16137</v>
+        <v>12970</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3854</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>7921</v>
+        <v>4057</v>
       </c>
       <c r="D4" t="n">
-        <v>14884</v>
+        <v>11701</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1617</v>
+        <v>351</v>
       </c>
       <c r="C5" t="n">
-        <v>11140</v>
+        <v>4370</v>
       </c>
       <c r="D5" t="n">
-        <v>7128</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>527</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>6812</v>
+        <v>5013</v>
       </c>
       <c r="D6" t="n">
-        <v>2100</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>217</v>
       </c>
       <c r="C7" t="n">
-        <v>2588</v>
+        <v>4783</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>931</v>
+        <v>3261</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>1543</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>540</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7206</v>
+        <v>3036</v>
       </c>
       <c r="C2" t="n">
-        <v>5943</v>
+        <v>5440</v>
       </c>
       <c r="D2" t="n">
-        <v>14749</v>
+        <v>15567</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3241</v>
+        <v>723</v>
       </c>
       <c r="C3" t="n">
-        <v>2121</v>
+        <v>2836</v>
       </c>
       <c r="D3" t="n">
-        <v>1599</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5104</v>
+        <v>2031</v>
       </c>
       <c r="C2" t="n">
-        <v>6755</v>
+        <v>3448</v>
       </c>
       <c r="D2" t="n">
-        <v>23683</v>
+        <v>24721</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4293</v>
+        <v>1594</v>
       </c>
       <c r="C3" t="n">
-        <v>3741</v>
+        <v>3781</v>
       </c>
       <c r="D3" t="n">
-        <v>3690</v>
+        <v>4797</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1441</v>
+        <v>362</v>
       </c>
       <c r="C4" t="n">
-        <v>1285</v>
+        <v>1817</v>
       </c>
       <c r="D4" t="n">
-        <v>1503</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4937</v>
+        <v>1093</v>
       </c>
       <c r="C2" t="n">
-        <v>5470</v>
+        <v>3728</v>
       </c>
       <c r="D2" t="n">
-        <v>25515</v>
+        <v>29843</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3866</v>
+        <v>1496</v>
       </c>
       <c r="C3" t="n">
-        <v>4660</v>
+        <v>3080</v>
       </c>
       <c r="D3" t="n">
-        <v>6623</v>
+        <v>7791</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2430</v>
+        <v>857</v>
       </c>
       <c r="C4" t="n">
-        <v>2649</v>
+        <v>2967</v>
       </c>
       <c r="D4" t="n">
-        <v>1877</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>651</v>
+        <v>203</v>
       </c>
       <c r="C5" t="n">
-        <v>796</v>
+        <v>1145</v>
       </c>
       <c r="D5" t="n">
-        <v>1196</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5888</v>
+        <v>844</v>
       </c>
       <c r="C2" t="n">
-        <v>6177</v>
+        <v>4997</v>
       </c>
       <c r="D2" t="n">
-        <v>33652</v>
+        <v>32396</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3602</v>
+        <v>1074</v>
       </c>
       <c r="C3" t="n">
-        <v>4418</v>
+        <v>2972</v>
       </c>
       <c r="D3" t="n">
-        <v>9028</v>
+        <v>10758</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2686</v>
+        <v>1016</v>
       </c>
       <c r="C4" t="n">
-        <v>3649</v>
+        <v>2970</v>
       </c>
       <c r="D4" t="n">
-        <v>2685</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1268</v>
+        <v>449</v>
       </c>
       <c r="C5" t="n">
-        <v>1757</v>
+        <v>2135</v>
       </c>
       <c r="D5" t="n">
-        <v>1265</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>343</v>
+        <v>144</v>
       </c>
       <c r="C6" t="n">
-        <v>550</v>
+        <v>732</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8334</v>
+        <v>1844</v>
       </c>
       <c r="C2" t="n">
-        <v>5918</v>
+        <v>6129</v>
       </c>
       <c r="D2" t="n">
-        <v>40970</v>
+        <v>24757</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3422</v>
+        <v>799</v>
       </c>
       <c r="C3" t="n">
-        <v>4355</v>
+        <v>3545</v>
       </c>
       <c r="D3" t="n">
-        <v>11416</v>
+        <v>13289</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1940</v>
+        <v>906</v>
       </c>
       <c r="C4" t="n">
-        <v>3308</v>
+        <v>2880</v>
       </c>
       <c r="D4" t="n">
-        <v>3260</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1034</v>
+        <v>626</v>
       </c>
       <c r="C5" t="n">
-        <v>2017</v>
+        <v>2539</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>385</v>
+        <v>262</v>
       </c>
       <c r="C6" t="n">
-        <v>780</v>
+        <v>1451</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>284</v>
+        <v>516</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6650</v>
+        <v>1795</v>
       </c>
       <c r="C2" t="n">
-        <v>10766</v>
+        <v>11670</v>
       </c>
       <c r="D2" t="n">
-        <v>37359</v>
+        <v>36381</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4903</v>
+        <v>1046</v>
       </c>
       <c r="C3" t="n">
-        <v>4576</v>
+        <v>4228</v>
       </c>
       <c r="D3" t="n">
-        <v>15540</v>
+        <v>14096</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2355</v>
+        <v>745</v>
       </c>
       <c r="C4" t="n">
-        <v>3840</v>
+        <v>3171</v>
       </c>
       <c r="D4" t="n">
-        <v>4773</v>
+        <v>5935</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1320</v>
+        <v>675</v>
       </c>
       <c r="C5" t="n">
-        <v>2743</v>
+        <v>2659</v>
       </c>
       <c r="D5" t="n">
-        <v>1581</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>662</v>
+        <v>385</v>
       </c>
       <c r="C6" t="n">
-        <v>1482</v>
+        <v>1968</v>
       </c>
       <c r="D6" t="n">
-        <v>827</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>565</v>
+        <v>959</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>256</v>
+        <v>401</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5609</v>
+        <v>1587</v>
       </c>
       <c r="C2" t="n">
-        <v>9209</v>
+        <v>7002</v>
       </c>
       <c r="D2" t="n">
-        <v>42386</v>
+        <v>28366</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4737</v>
+        <v>1374</v>
       </c>
       <c r="C3" t="n">
-        <v>6882</v>
+        <v>7397</v>
       </c>
       <c r="D3" t="n">
-        <v>17912</v>
+        <v>15865</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3090</v>
+        <v>623</v>
       </c>
       <c r="C4" t="n">
-        <v>4176</v>
+        <v>4592</v>
       </c>
       <c r="D4" t="n">
-        <v>6695</v>
+        <v>5466</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1621</v>
+        <v>355</v>
       </c>
       <c r="C5" t="n">
-        <v>3286</v>
+        <v>1928</v>
       </c>
       <c r="D5" t="n">
-        <v>2099</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>897</v>
+        <v>151</v>
       </c>
       <c r="C6" t="n">
-        <v>2116</v>
+        <v>939</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>86</v>
+      </c>
+      <c r="C7" t="n">
         <v>392</v>
       </c>
-      <c r="C7" t="n">
-        <v>1050</v>
-      </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>413</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
